--- a/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_IGNACIO</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.390611</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.90747500000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>357</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.390611</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.907475</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>125</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.146879</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.998696</v>
-      </c>
-      <c r="I3" t="n">
-        <v>343</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.146879</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.998696</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>16458</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.214353</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.968675</v>
-      </c>
-      <c r="I4" t="n">
-        <v>211</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.214353</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.968675</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>16467</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.136149</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.989132</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.136149</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.989132</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>16624 DEFENSORES DEL SANTUARIO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.192134</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.083906</v>
-      </c>
-      <c r="I6" t="n">
-        <v>252</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.192134</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.083906</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>16631</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.154918</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.05238</v>
-      </c>
-      <c r="I7" t="n">
-        <v>209</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.154918</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.05238</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>16877</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.180805</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.905309</v>
-      </c>
-      <c r="I8" t="n">
-        <v>204</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.180805</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.905309</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>17623</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.087779</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.07387199999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>249</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.087779</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.073872</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>16449 ELOY SOBERON FLORES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.148761</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.002111</v>
-      </c>
-      <c r="I10" t="n">
-        <v>938</v>
-      </c>
-      <c r="J10" t="n">
-        <v>49</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.148761</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.002111</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>16462 SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.143979</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.004561</v>
-      </c>
-      <c r="I11" t="n">
-        <v>755</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.143979</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.004561</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>16466 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.099097</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.045486</v>
-      </c>
-      <c r="I12" t="n">
-        <v>284</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.099097</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.045486</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>16470 SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.145804</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.003186</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1388</v>
-      </c>
-      <c r="J13" t="n">
-        <v>65</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.145804</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.003186</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>TITO CUSY YUPANQUI</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.146826</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.002686</v>
-      </c>
-      <c r="I14" t="n">
-        <v>818</v>
-      </c>
-      <c r="J14" t="n">
-        <v>50</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.146826</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.002686</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>16450 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.145686</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.007102</v>
-      </c>
-      <c r="I15" t="n">
-        <v>840</v>
-      </c>
-      <c r="J15" t="n">
-        <v>35</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.145686</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.007102</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>101</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.145671</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.00609799999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>510</v>
-      </c>
-      <c r="J16" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.145671</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.006098</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>16485</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.300475</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.90034300000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>288</v>
-      </c>
-      <c r="J17" t="n">
-        <v>14</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.300475</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.900343</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>16501 JUAN ALBACETE SAIZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.308091</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.755385</v>
-      </c>
-      <c r="I18" t="n">
-        <v>328</v>
-      </c>
-      <c r="J18" t="n">
-        <v>24</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.308091</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.755385</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>16498 TUPAC AMARU II</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.270679</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.77287800000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>447</v>
-      </c>
-      <c r="J19" t="n">
-        <v>34</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.270679</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.772878</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>16502</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.188758</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.77283799999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>231</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.188758</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.772838</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>16506 SAN JOSE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.28518</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.807061</v>
-      </c>
-      <c r="I21" t="n">
-        <v>380</v>
-      </c>
-      <c r="J21" t="n">
-        <v>31</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.28518</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.807061</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>16641 PEDRO PAULET</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.193049</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.798575</v>
-      </c>
-      <c r="I22" t="n">
-        <v>211</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.193049</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.798575</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>16642</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.340161</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.682018</v>
-      </c>
-      <c r="I23" t="n">
-        <v>297</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.340161</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.682018</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>16471</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.393048</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.907263</v>
-      </c>
-      <c r="I24" t="n">
-        <v>263</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.393048</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.907263</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>16480 ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.377622</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-79.01399000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>428</v>
-      </c>
-      <c r="J25" t="n">
-        <v>30</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.377622</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.01399</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>16646</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.105107</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.11524300000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>246</v>
-      </c>
-      <c r="J26" t="n">
-        <v>16</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.105107</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.115243</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>17641</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.101937</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.16499</v>
-      </c>
-      <c r="I27" t="n">
-        <v>279</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.101937</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.16499</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>16512 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.030214</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.157431</v>
-      </c>
-      <c r="I28" t="n">
-        <v>224</v>
-      </c>
-      <c r="J28" t="n">
-        <v>14</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.030214</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.157431</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>126523</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CESAR ABRAHAM VALLEJO</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.390611</t>
+          <t>-5.136149</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.907475</t>
+          <t>-78.989132</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>126288</t>
+          <t>126716</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.146879</t>
+          <t>-5.180805</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.998696</t>
+          <t>-78.905309</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>126467</t>
+          <t>126288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.214353</t>
+          <t>-5.146879</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.968675</t>
+          <t>-78.998696</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>126523</t>
+          <t>127315</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.136149</t>
+          <t>-5.300475</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.989132</t>
+          <t>-78.900343</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>126556</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16624 DEFENSORES DEL SANTUARIO</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.192134</t>
+          <t>-5.393048</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.083906</t>
+          <t>-78.907263</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>126603</t>
+          <t>129630</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16512 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.154918</t>
+          <t>-5.030214</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.05238</t>
+          <t>-79.157431</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>126716</t>
+          <t>126467</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.180805</t>
+          <t>-5.214353</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.905309</t>
+          <t>-78.968675</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>16624 DEFENSORES DEL SANTUARIO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.087779</t>
+          <t>-5.192134</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.073872</t>
+          <t>-79.083906</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>127037</t>
+          <t>126603</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16449 ELOY SOBERON FLORES</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.148761</t>
+          <t>-5.154918</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.002111</t>
+          <t>-79.05238</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>128447</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16462 SAN JUAN BOSCO</t>
+          <t>16641 PEDRO PAULET</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.143979</t>
+          <t>-5.193049</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.004561</t>
+          <t>-78.798575</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>127075</t>
+          <t>128452</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16466 SAN FRANCISCO DE ASIS</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.099097</t>
+          <t>-5.340161</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.045486</t>
+          <t>-78.682018</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>129569</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16470 SAN IGNACIO DE LOYOLA</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.145804</t>
+          <t>-5.101937</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.003186</t>
+          <t>-79.16499</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>127221</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TITO CUSY YUPANQUI</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.146826</t>
+          <t>-5.188758</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.002686</t>
+          <t>-78.772838</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>127235</t>
+          <t>129418</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16450 NUESTRA SEÑORA DE FATIMA</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.145686</t>
+          <t>-5.105107</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.007102</t>
+          <t>-79.115243</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>127240</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.145671</t>
+          <t>-5.087779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.006098</t>
+          <t>-79.073872</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>127075</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16466 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.300475</t>
+          <t>-5.099097</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.900343</t>
+          <t>-79.045486</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>127933</t>
+          <t>127240</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16501 JUAN ALBACETE SAIZ</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.308091</t>
+          <t>-5.145671</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.755385</t>
+          <t>-79.006098</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>128391</t>
+          <t>127933</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16498 TUPAC AMARU II</t>
+          <t>16501 JUAN ALBACETE SAIZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.270679</t>
+          <t>-5.308091</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.772878</t>
+          <t>-78.755385</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>128428</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.188758</t>
+          <t>-5.390611</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.772838</t>
+          <t>-78.907475</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>128433</t>
+          <t>129201</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16506 SAN JOSE</t>
+          <t>16480 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.28518</t>
+          <t>-5.377622</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.807061</t>
+          <t>-79.01399</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>128447</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16641 PEDRO PAULET</t>
+          <t>16506 SAN JOSE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.193049</t>
+          <t>-5.28518</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.798575</t>
+          <t>-78.807061</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>380</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>128452</t>
+          <t>128391</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16498 TUPAC AMARU II</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.340161</t>
+          <t>-5.270679</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.682018</t>
+          <t>-78.772878</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>127235</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16450 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.393048</t>
+          <t>-5.145686</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.907263</t>
+          <t>-79.007102</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>840</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>129201</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16480 ANTONIO RAYMONDI</t>
+          <t>16462 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.377622</t>
+          <t>-5.143979</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.01399</t>
+          <t>-79.004561</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>755</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>129418</t>
+          <t>127037</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>16449 ELOY SOBERON FLORES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.105107</t>
+          <t>-5.148761</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.115243</t>
+          <t>-79.002111</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>127221</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>TITO CUSY YUPANQUI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.101937</t>
+          <t>-5.146826</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.16499</t>
+          <t>-79.002686</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>818</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>129630</t>
+          <t>127080</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16512 ALMIRANTE MIGUEL GRAU</t>
+          <t>16470 SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.030214</t>
+          <t>-5.145804</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.157431</t>
+          <t>-79.003186</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>126523</t>
+          <t>129630</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16512 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.136149</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.989132</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-5.030214</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-79.157431</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>126716</t>
+          <t>129569</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.180805</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.905309</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-5.101937</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.16499</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>126288</t>
+          <t>129418</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.146879</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.998696</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-5.105107</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.115243</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>129201</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16480 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.300475</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.900343</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-5.377622</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.01399</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -759,22 +759,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>-5.393048</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-78.907263</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>129630</t>
+          <t>128452</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16512 ALMIRANTE MIGUEL GRAU</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.030214</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.157431</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-5.340161</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.682018</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>126467</t>
+          <t>128447</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16641 PEDRO PAULET</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.214353</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.968675</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-5.193049</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.798575</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>126556</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16624 DEFENSORES DEL SANTUARIO</t>
+          <t>16506 SAN JOSE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.192134</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.083906</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-5.28518</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.807061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>126603</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.154918</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.05238</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-5.188758</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.772838</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128447</t>
+          <t>128391</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16641 PEDRO PAULET</t>
+          <t>16498 TUPAC AMARU II</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.193049</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.798575</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-5.270679</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.772878</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>128452</t>
+          <t>127933</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16501 JUAN ALBACETE SAIZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.340161</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.682018</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-5.308091</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.755385</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>127315</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.101937</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.16499</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-5.300475</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.900343</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>128428</t>
+          <t>127240</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.188758</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.772838</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-5.145671</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.006098</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>129418</t>
+          <t>127235</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>16450 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.105107</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.115243</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-5.145686</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.007102</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>127221</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>TITO CUSY YUPANQUI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.087779</t>
+          <t>818</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.073872</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-5.146826</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.002686</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>127075</t>
+          <t>127080</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16466 SAN FRANCISCO DE ASIS</t>
+          <t>16470 SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.099097</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.045486</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-5.145804</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.003186</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>127240</t>
+          <t>127075</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>16466 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.145671</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.006098</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-5.099097</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.045486</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>127933</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16501 JUAN ALBACETE SAIZ</t>
+          <t>16462 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.308091</t>
+          <t>755</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.755385</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-5.143979</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.004561</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>127037</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CESAR ABRAHAM VALLEJO</t>
+          <t>16449 ELOY SOBERON FLORES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.390611</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.907475</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-5.148761</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.002111</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>129201</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16480 ANTONIO RAYMONDI</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.377622</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.01399</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-5.087779</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.073872</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>128433</t>
+          <t>126716</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16506 SAN JOSE</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.28518</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.807061</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>-5.180805</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.905309</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>128391</t>
+          <t>126603</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16498 TUPAC AMARU II</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.270679</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.772878</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-5.154918</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.05238</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>127235</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16450 NUESTRA SEÑORA DE FATIMA</t>
+          <t>16624 DEFENSORES DEL SANTUARIO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.145686</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.007102</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>-5.192134</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.083906</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>126523</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16462 SAN JUAN BOSCO</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.143979</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.004561</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>-5.136149</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.989132</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>127037</t>
+          <t>126467</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16449 ELOY SOBERON FLORES</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.148761</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.002111</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-5.214353</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-78.968675</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>127221</t>
+          <t>126288</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TITO CUSY YUPANQUI</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.146826</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.002686</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>-5.146879</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-78.998696</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>012319</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16470 SAN IGNACIO DE LOYOLA</t>
+          <t>CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.145804</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.003186</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>-5.390611</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-78.907475</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-SAN_IGNACIO-SAN_IGNACIO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
